--- a/naver-place-crawler/results_derma/금정구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/금정구_피부과.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q2" t="n">
-        <v>739</v>
+        <v>1054</v>
       </c>
       <c r="R2" t="n">
-        <v>1161</v>
+        <v>1479</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제니크의원 부산대점</t>
+          <t>단스위티의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pollen0514@naver.com</t>
+          <t>dansweetie@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-583-8585</t>
+          <t>051-925-9595</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로 49 4층</t>
+          <t>부산광역시 금정구 장전온천천로 51 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.jennyque.kr/</t>
+          <t>http://www.dansweetie.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>230</v>
+        <v>1978</v>
       </c>
       <c r="Q3" t="n">
-        <v>52</v>
+        <v>289</v>
       </c>
       <c r="R3" t="n">
-        <v>282</v>
+        <v>2267</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1881632977</t>
+          <t>1725775115</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881632977</t>
+          <t>https://m.place.naver.com/place/1725775115</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>단스위티의원</t>
+          <t>제니크의원 부산대점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dansweetie@naver.com</t>
+          <t>pollen0514@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-925-9595</t>
+          <t>051-583-8585</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 장전온천천로 51 4층</t>
+          <t>부산광역시 금정구 부산대학로 49 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.dansweetie.com/</t>
+          <t>https://www.jennyque.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1934</v>
+        <v>237</v>
       </c>
       <c r="Q4" t="n">
-        <v>288</v>
+        <v>52</v>
       </c>
       <c r="R4" t="n">
-        <v>2222</v>
+        <v>289</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1725775115</t>
+          <t>1881632977</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725775115</t>
+          <t>https://m.place.naver.com/place/1881632977</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -906,10 +906,10 @@
         <v>811</v>
       </c>
       <c r="Q5" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="R5" t="n">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>미의원</t>
+          <t>아카데미휴먼피부과의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>meclinic-gwangju@naver.com</t>
+          <t>academyderma@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>051-518-5761</t>
+          <t>0507-1417-7577</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로 83 2층 미의원</t>
+          <t>부산광역시 금정구 구서로 10 우지메디컬 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://academydermatology.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>353</v>
+        <v>750</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>473</v>
       </c>
       <c r="R6" t="n">
-        <v>373</v>
+        <v>1223</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1934050331</t>
+          <t>1816791091</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934050331</t>
+          <t>https://m.place.naver.com/place/1816791091</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q7" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="R7" t="n">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,56 +1116,56 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부과</t>
+          <t>외과</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아카데미휴먼피부과의원</t>
+          <t>열린외과병원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>academyderma@naver.com</t>
+          <t>indijohns@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-7577</t>
+          <t>0507-1492-0716</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 10 우지메디컬 4층</t>
+          <t>경기 안산시 단원구 화랑로 376 지하1층, 지상2, 3, 4층(안산시청,단원경찰서앞)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://academydermatology.co.kr/</t>
+          <t>https://ansan-burn.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>751</v>
+        <v>681</v>
       </c>
       <c r="Q8" t="n">
-        <v>467</v>
+        <v>366</v>
       </c>
       <c r="R8" t="n">
-        <v>1218</v>
+        <v>1047</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1816791091</t>
+          <t>35751400</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816791091</t>
+          <t>https://m.place.naver.com/place/35751400</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
